--- a/板间通讯协议.xlsx
+++ b/板间通讯协议.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="64">
   <si>
     <t>主板发送can通道</t>
   </si>
@@ -180,6 +180,45 @@
   </si>
   <si>
     <t>rc_ch3</t>
+  </si>
+  <si>
+    <t>电机0</t>
+  </si>
+  <si>
+    <t>按键0</t>
+  </si>
+  <si>
+    <t>电机1</t>
+  </si>
+  <si>
+    <t>按键1</t>
+  </si>
+  <si>
+    <t>电机2</t>
+  </si>
+  <si>
+    <t>按键2</t>
+  </si>
+  <si>
+    <t>电机3</t>
+  </si>
+  <si>
+    <t>电机4</t>
+  </si>
+  <si>
+    <t>电机5</t>
+  </si>
+  <si>
+    <t>电机6</t>
+  </si>
+  <si>
+    <t>电机7</t>
+  </si>
+  <si>
+    <t>电机8</t>
+  </si>
+  <si>
+    <t>电机9</t>
   </si>
 </sst>
 </file>
@@ -1345,7 +1384,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="20.3916666666667" style="2" customWidth="1"/>
@@ -1719,7 +1758,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="33" spans="3:6">
+    <row r="33" spans="2:6">
       <c r="C33" s="2">
         <v>4</v>
       </c>
@@ -1733,7 +1772,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="34" spans="3:6">
+    <row r="34" spans="2:6">
       <c r="C34" s="2">
         <v>5</v>
       </c>
@@ -1741,7 +1780,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="3:6">
+    <row r="35" spans="2:6">
       <c r="C35" s="2">
         <v>6</v>
       </c>
@@ -1755,12 +1794,71 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="3:6">
+    <row r="36" spans="2:6">
       <c r="C36" s="2">
         <v>7</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="49" spans="2:2">
+      <c r="B49" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
   </sheetData>
